--- a/datos/info_mupi.xlsx
+++ b/datos/info_mupi.xlsx
@@ -1,111 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE7FB43-4C0B-C949-A655-F209A4DF19CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="18480" xr2:uid="{19026AE3-6B4F-45D3-8604-4731C2D808B9}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="18480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Nombre evento</t>
-  </si>
-  <si>
-    <t>Lugar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horario </t>
-  </si>
-  <si>
-    <t>Living Trends</t>
-  </si>
-  <si>
-    <t>Auditorio + Terraza C81</t>
-  </si>
-  <si>
-    <t>Con clientes</t>
-  </si>
-  <si>
-    <t>Property &amp; Facility Management Summit</t>
-  </si>
-  <si>
-    <t>Eurostar Suites Mirasierra de Madrid</t>
-  </si>
-  <si>
-    <t>Participación</t>
-  </si>
-  <si>
-    <t>¿Quién participa?</t>
-  </si>
-  <si>
-    <t>Tipo de evento</t>
-  </si>
-  <si>
-    <t>Alfonso Arroyo</t>
-  </si>
-  <si>
-    <t>Link QR</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -137,29 +69,94 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -478,94 +475,694 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
-  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences>
-    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED011342-C7D1-41BA-9CA2-E06902A80352}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col width="33.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.6640625" customWidth="1" min="2" max="2"/>
+    <col width="30.1640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.1640625" customWidth="1" min="4" max="4"/>
+    <col width="12.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="14" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>42630</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Nombre evento</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Lugar</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horario </t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de evento</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>¿Quién participa?</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Link QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Living Trends</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Auditorio + Terraza C81</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Con clientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Desayuno de bienvenida a nuevas incorporaciones</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comedor corporativo · Planta 0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>09:00 - 10:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/desayuno-bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Formación: nuevo gestor documental</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aula 2 · Planta 3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12:00 - 13:30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Formación</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Marta Ruiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Comité de marca trimestral</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sala de Consejo · Planta 6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10:00 - 12:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dirección de Marca</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Afterwork de septiembre</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Terraza · Planta 7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19:00 - 21:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/afterwork-septiembre</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Visita al showroom de la promoción Chamartín</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Showroom · Calle Mayor 14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Con clientes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Equipo Comercial</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/visita-showroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chequeo médico anual</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sala Médica · Planta -1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>09:00 - 14:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/chequeo-medico</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Comité de dirección ampliado</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sala de Consejo · Planta 6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>08:30 - 10:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dirección General</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Taller de prototipado con clientes</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hub de Innovación · Planta 5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10:30 - 12:30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Con clientes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lucía Ferrer; Diego Pardo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/taller-prototipado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mesa redonda sobre urbanismo MAPIC</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Auditorio · Planta 0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13:00 - 14:30</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Participación</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Alfonso Arroyo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/mesa-urbanismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Formación en herramientas de reporting</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aula 1 · Planta 3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16:00 - 17:30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Formación</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diego Pardo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/formacion-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cata de vinos con el equipo comercial</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Terraza · Planta 7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>19:00 - 21:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/cata-vinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Café con innovación: tendencias PropTech</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hub de Innovación · Planta 5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>08:30 - 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lucía Ferrer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/cafe-proptech</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Demo de gemelo digital de edificio</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hub de Innovación · Planta 5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11:00 - 12:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Equipo de Innovación</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/demo-gemelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sesión de yoga en la terraza</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Terraza · Planta 7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>18:00 - 19:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/yoga-terraza</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Presentación de la cartera de activos a inversores institucionales</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Auditorio · Planta 0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>12:00 - 13:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Con clientes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dirección General; Relación con Inversores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/cartera-inversores</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jornada de puertas abiertas</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Todo el edificio</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Participación</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Comunicación Interna</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/puertas-abiertas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Taller de ergonomía en el puesto</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sala Polivalente · Planta 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16:00 - 17:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ana Sarabia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://example.com/registro/ergonomia-puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inventario anual de espacios</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Todo el edificio</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>09:30 - 18:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Facility Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Property &amp; Facility Management Summit</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
         <v>46309</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eurostar Suites Mirasierra de Madrid</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Participación</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Alfonso Arroyo</t>
+        </is>
       </c>
     </row>
   </sheetData>
